--- a/data/shopweb.xlsx
+++ b/data/shopweb.xlsx
@@ -1,43 +1,195 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr codeName="ThisWorkbook"/>
+  <s:bookViews>
+    <s:workbookView activeTab="8"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="login" sheetId="1" r:id="rId1"/>
+    <s:sheet name="getDataList" sheetId="2" r:id="rId2"/>
+    <s:sheet name="getChatVedio" sheetId="3" r:id="rId3"/>
+    <s:sheet name="getOrderTempleData" sheetId="4" r:id="rId4"/>
+    <s:sheet name="getOrderList" sheetId="5" r:id="rId5"/>
+    <s:sheet name="saveOfflineOrder" sheetId="6" r:id="rId6"/>
+    <s:sheet name="getDataList1" sheetId="7" r:id="rId7"/>
+    <s:sheet name="getOfflineOrderInfo" sheetId="8" r:id="rId8"/>
+    <s:sheet name="getDataList2" sheetId="9" r:id="rId9"/>
+  </s:sheets>
+  <s:definedNames/>
+  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
+</s:workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+  <si>
+    <t>case_id</t>
+  </si>
+  <si>
+    <t>interface</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>管理员登录-登陆成功</t>
+  </si>
+  <si>
+    <t>post</t>
+  </si>
+  <si>
+    <t>/index/login</t>
+  </si>
+  <si>
+    <t>{"username": "#shop_user#","password": '#shop_pwd#'}</t>
+  </si>
+  <si>
+    <t>{"result": "0000"}</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>getDataList</t>
+  </si>
+  <si>
+    <t>获取处方单列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/InquiryOrder/getDataList?start=2019-10-11&amp;end=2020-5-11&amp;shop=&amp;doctor=&amp;type=1&amp;ordercode=</t>
+  </si>
+  <si>
+    <t>{'length':10,'search':'','start':0,'page':1}</t>
+  </si>
+  <si>
+    <t>{"draw": "1"}</t>
+  </si>
+  <si>
+    <t>getChatVedio</t>
+  </si>
+  <si>
+    <t>查看视频记录-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/InquiryOrder/getChatVedio</t>
+  </si>
+  <si>
+    <t>{"roomId": "880671125"}</t>
+  </si>
+  <si>
+    <t>{"CODE": "0000"}</t>
+  </si>
+  <si>
+    <t>获取处方数据-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/InquiryOrder/getOrderTempleData</t>
+  </si>
+  <si>
+    <t>{"id": "9e0ab24d6f9e6f38770d4027dfc051ab",'orderType':2}</t>
+  </si>
+  <si>
+    <t>{"ORGGUID": "186990"}</t>
+  </si>
+  <si>
+    <t>获取待确认问诊列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/ReplenishOrder/getOrderList?startTime=2019-10-17&amp;endTime=2020-5-11</t>
+  </si>
+  <si>
+    <t>saveOfflineOrder</t>
+  </si>
+  <si>
+    <t>提交处方-提交成功</t>
+  </si>
+  <si>
+    <t>/ShopUpload/saveOfflineOrder</t>
+  </si>
+  <si>
+    <t>{"img":"http://yxtdoctor-1252032681.cos.ap-guangzhou.myqcloud.com/1571376102013-A9955C0F-96E4-4526-A322-E825C08099C4.jpg","page":1,"type":1,"personal_name":"李四","personal_sex":1,"personal_id_card":"","personal_age":11,"personal_phone":1111,"personal_hospital":"","personal_doctor":"","personal_department":"","personal_prescribe_date":"","personal_date":"","personal_diagnosis":"","personal_note":"","personal_kind":"normal","phone":"","id":100002,"USAGE":"口服","DAYS":1,"COUNTS":1,"UNITIDS":"粒","TIMES":1,"NUMBER":1,"goodsurlsmall":"","goodsname":"头孢克肟胶囊","spec":"100mg*10粒","IFALLERGIC":2,"goodsprice":"undefined"}</t>
+  </si>
+  <si>
+    <t>外来问诊处方列表-获取成功</t>
+  </si>
+  <si>
+    <t>/shopExamine/getDataList</t>
+  </si>
+  <si>
+    <t>getOfflineOrderInfo</t>
+  </si>
+  <si>
+    <t>获取处方详情-获取成功</t>
+  </si>
+  <si>
+    <t>/ShopExamine/getOfflineOrderInfo</t>
+  </si>
+  <si>
+    <t>{'ordercode':'000003|20191021161535302'}</t>
+  </si>
+  <si>
+    <t>获取挂单列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/Posbillquery/getDataList</t>
+  </si>
+  <si>
+    <t>{'shopCode':'003'}</t>
+  </si>
+  <si>
+    <t>{"Code": 0}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,26 +197,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" builtinId="0" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -330,10 +495,683 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="11.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="52.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14.75" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="24.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="11.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="31.875" customWidth="1" min="6" max="6"/>
+    <col width="14.75" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="32.625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="22.25" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14.75" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="39.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="53.625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="21" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="28.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="39.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="33.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="11.125" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="15.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="28.625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="98" customWidth="1" min="6" max="6"/>
+    <col width="15.125" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="24.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="24.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="33.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="11.125" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="32" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="39.25" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15.125" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="29.875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="15.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
 </file>
--- a/data/shopweb.xlsx
+++ b/data/shopweb.xlsx
@@ -3,7 +3,7 @@
 <s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr codeName="ThisWorkbook"/>
   <s:bookViews>
-    <s:workbookView activeTab="8"/>
+    <s:workbookView activeTab="0"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="login" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <t>login</t>
   </si>
   <si>
-    <t>管理员登录-登陆成功</t>
+    <t>门店登录-登陆成功</t>
   </si>
   <si>
     <t>post</t>
